--- a/datos-prueba/padron-prueba-errores.xlsx
+++ b/datos-prueba/padron-prueba-errores.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -743,17 +743,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>45871238</t>
+          <t>45871236</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SIN METRAJE APAZA</t>
+          <t>DNI DUPLICADO CHOQUE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ERR-C-006</t>
+          <t>ERR-C-007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -791,17 +791,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>45871236</t>
+          <t>45871239</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNI DUPLICADO CHOQUE</t>
+          <t>CODIGO DUPLICADO HUANCA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERR-C-007</t>
+          <t>ERR-C-001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>45871239</t>
+          <t>45871240</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CODIGO DUPLICADO HUANCA</t>
+          <t>RUBRO INEXISTENTE PARI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ERR-C-001</t>
+          <t>ERR-C-009</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -869,61 +869,13 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ropa</t>
+          <t>ferreteria</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>Presente</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>45871240</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>RUBRO INEXISTENTE PARI</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ERR-C-009</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bloque C - Fila 1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Zona Norte</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ferial</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ferreteria</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Presente</t>
         </is>

--- a/datos-prueba/padron-prueba-errores.xlsx
+++ b/datos-prueba/padron-prueba-errores.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -59,13 +61,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -444,6 +447,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,6 +508,11 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Fecha Feria</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -552,6 +561,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -596,6 +606,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -644,6 +655,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -692,6 +704,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -736,6 +749,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -784,6 +798,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -832,6 +847,7 @@
           <t>Presente</t>
         </is>
       </c>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -879,6 +895,107 @@
         <is>
           <t>Presente</t>
         </is>
+      </c>
+      <c r="K10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>45871241</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AUSENTE SIN FECHA COAQUIRA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ERR-C-010</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bloque C - Fila 1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Zona Norte</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ferial</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ropa</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ausente</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>45871242</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FECHA NO ES FERIA LAYME</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ERR-C-011</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bloque C - Fila 1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Zona Norte</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ferial</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ropa</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>46317</v>
       </c>
     </row>
   </sheetData>

--- a/datos-prueba/padron-prueba-errores.xlsx
+++ b/datos-prueba/padron-prueba-errores.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +514,11 @@
           <t>Fecha Feria</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Tarifa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -996,6 +1002,60 @@
       </c>
       <c r="K12" s="4" t="n">
         <v>46317</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>45871243</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TARIFA INEXISTENTE VILCA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ERR-C-012</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bloque C - Fila 1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Zona Norte</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ferial</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ropa</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Presente</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Pista de tierra</t>
+        </is>
       </c>
     </row>
   </sheetData>
